--- a/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/finassetliabilitystatement/FinAssetLiabilityStatement.xlsx
+++ b/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/finassetliabilitystatement/FinAssetLiabilityStatement.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20373"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3EF011-AEB2-46CB-9412-DEFECBE8903D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90916A79-71C0-4FFE-AD7D-98BCBF455FC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>${title}</t>
   </si>
@@ -77,6 +77,10 @@
   </si>
   <si>
     <t>#{mergeList.initialBalance1}</t>
+  </si>
+  <si>
+    <t>${platDate}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -84,9 +88,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,11 +121,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -130,16 +142,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -147,16 +162,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -239,49 +244,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -625,106 +630,421 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="30.875" style="1" customWidth="1"/>
-    <col min="2" max="3" width="20.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="30.875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="20.625" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="30.875" style="5" customWidth="1"/>
+    <col min="2" max="3" width="20.625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="30.875" style="5" customWidth="1"/>
+    <col min="5" max="6" width="20.625" style="5" customWidth="1"/>
+    <col min="7" max="256" width="9" style="5"/>
+    <col min="257" max="257" width="30.875" style="5" customWidth="1"/>
+    <col min="258" max="259" width="20.625" style="5" customWidth="1"/>
+    <col min="260" max="260" width="30.875" style="5" customWidth="1"/>
+    <col min="261" max="262" width="20.625" style="5" customWidth="1"/>
+    <col min="263" max="512" width="9" style="5"/>
+    <col min="513" max="513" width="30.875" style="5" customWidth="1"/>
+    <col min="514" max="515" width="20.625" style="5" customWidth="1"/>
+    <col min="516" max="516" width="30.875" style="5" customWidth="1"/>
+    <col min="517" max="518" width="20.625" style="5" customWidth="1"/>
+    <col min="519" max="768" width="9" style="5"/>
+    <col min="769" max="769" width="30.875" style="5" customWidth="1"/>
+    <col min="770" max="771" width="20.625" style="5" customWidth="1"/>
+    <col min="772" max="772" width="30.875" style="5" customWidth="1"/>
+    <col min="773" max="774" width="20.625" style="5" customWidth="1"/>
+    <col min="775" max="1024" width="9" style="5"/>
+    <col min="1025" max="1025" width="30.875" style="5" customWidth="1"/>
+    <col min="1026" max="1027" width="20.625" style="5" customWidth="1"/>
+    <col min="1028" max="1028" width="30.875" style="5" customWidth="1"/>
+    <col min="1029" max="1030" width="20.625" style="5" customWidth="1"/>
+    <col min="1031" max="1280" width="9" style="5"/>
+    <col min="1281" max="1281" width="30.875" style="5" customWidth="1"/>
+    <col min="1282" max="1283" width="20.625" style="5" customWidth="1"/>
+    <col min="1284" max="1284" width="30.875" style="5" customWidth="1"/>
+    <col min="1285" max="1286" width="20.625" style="5" customWidth="1"/>
+    <col min="1287" max="1536" width="9" style="5"/>
+    <col min="1537" max="1537" width="30.875" style="5" customWidth="1"/>
+    <col min="1538" max="1539" width="20.625" style="5" customWidth="1"/>
+    <col min="1540" max="1540" width="30.875" style="5" customWidth="1"/>
+    <col min="1541" max="1542" width="20.625" style="5" customWidth="1"/>
+    <col min="1543" max="1792" width="9" style="5"/>
+    <col min="1793" max="1793" width="30.875" style="5" customWidth="1"/>
+    <col min="1794" max="1795" width="20.625" style="5" customWidth="1"/>
+    <col min="1796" max="1796" width="30.875" style="5" customWidth="1"/>
+    <col min="1797" max="1798" width="20.625" style="5" customWidth="1"/>
+    <col min="1799" max="2048" width="9" style="5"/>
+    <col min="2049" max="2049" width="30.875" style="5" customWidth="1"/>
+    <col min="2050" max="2051" width="20.625" style="5" customWidth="1"/>
+    <col min="2052" max="2052" width="30.875" style="5" customWidth="1"/>
+    <col min="2053" max="2054" width="20.625" style="5" customWidth="1"/>
+    <col min="2055" max="2304" width="9" style="5"/>
+    <col min="2305" max="2305" width="30.875" style="5" customWidth="1"/>
+    <col min="2306" max="2307" width="20.625" style="5" customWidth="1"/>
+    <col min="2308" max="2308" width="30.875" style="5" customWidth="1"/>
+    <col min="2309" max="2310" width="20.625" style="5" customWidth="1"/>
+    <col min="2311" max="2560" width="9" style="5"/>
+    <col min="2561" max="2561" width="30.875" style="5" customWidth="1"/>
+    <col min="2562" max="2563" width="20.625" style="5" customWidth="1"/>
+    <col min="2564" max="2564" width="30.875" style="5" customWidth="1"/>
+    <col min="2565" max="2566" width="20.625" style="5" customWidth="1"/>
+    <col min="2567" max="2816" width="9" style="5"/>
+    <col min="2817" max="2817" width="30.875" style="5" customWidth="1"/>
+    <col min="2818" max="2819" width="20.625" style="5" customWidth="1"/>
+    <col min="2820" max="2820" width="30.875" style="5" customWidth="1"/>
+    <col min="2821" max="2822" width="20.625" style="5" customWidth="1"/>
+    <col min="2823" max="3072" width="9" style="5"/>
+    <col min="3073" max="3073" width="30.875" style="5" customWidth="1"/>
+    <col min="3074" max="3075" width="20.625" style="5" customWidth="1"/>
+    <col min="3076" max="3076" width="30.875" style="5" customWidth="1"/>
+    <col min="3077" max="3078" width="20.625" style="5" customWidth="1"/>
+    <col min="3079" max="3328" width="9" style="5"/>
+    <col min="3329" max="3329" width="30.875" style="5" customWidth="1"/>
+    <col min="3330" max="3331" width="20.625" style="5" customWidth="1"/>
+    <col min="3332" max="3332" width="30.875" style="5" customWidth="1"/>
+    <col min="3333" max="3334" width="20.625" style="5" customWidth="1"/>
+    <col min="3335" max="3584" width="9" style="5"/>
+    <col min="3585" max="3585" width="30.875" style="5" customWidth="1"/>
+    <col min="3586" max="3587" width="20.625" style="5" customWidth="1"/>
+    <col min="3588" max="3588" width="30.875" style="5" customWidth="1"/>
+    <col min="3589" max="3590" width="20.625" style="5" customWidth="1"/>
+    <col min="3591" max="3840" width="9" style="5"/>
+    <col min="3841" max="3841" width="30.875" style="5" customWidth="1"/>
+    <col min="3842" max="3843" width="20.625" style="5" customWidth="1"/>
+    <col min="3844" max="3844" width="30.875" style="5" customWidth="1"/>
+    <col min="3845" max="3846" width="20.625" style="5" customWidth="1"/>
+    <col min="3847" max="4096" width="9" style="5"/>
+    <col min="4097" max="4097" width="30.875" style="5" customWidth="1"/>
+    <col min="4098" max="4099" width="20.625" style="5" customWidth="1"/>
+    <col min="4100" max="4100" width="30.875" style="5" customWidth="1"/>
+    <col min="4101" max="4102" width="20.625" style="5" customWidth="1"/>
+    <col min="4103" max="4352" width="9" style="5"/>
+    <col min="4353" max="4353" width="30.875" style="5" customWidth="1"/>
+    <col min="4354" max="4355" width="20.625" style="5" customWidth="1"/>
+    <col min="4356" max="4356" width="30.875" style="5" customWidth="1"/>
+    <col min="4357" max="4358" width="20.625" style="5" customWidth="1"/>
+    <col min="4359" max="4608" width="9" style="5"/>
+    <col min="4609" max="4609" width="30.875" style="5" customWidth="1"/>
+    <col min="4610" max="4611" width="20.625" style="5" customWidth="1"/>
+    <col min="4612" max="4612" width="30.875" style="5" customWidth="1"/>
+    <col min="4613" max="4614" width="20.625" style="5" customWidth="1"/>
+    <col min="4615" max="4864" width="9" style="5"/>
+    <col min="4865" max="4865" width="30.875" style="5" customWidth="1"/>
+    <col min="4866" max="4867" width="20.625" style="5" customWidth="1"/>
+    <col min="4868" max="4868" width="30.875" style="5" customWidth="1"/>
+    <col min="4869" max="4870" width="20.625" style="5" customWidth="1"/>
+    <col min="4871" max="5120" width="9" style="5"/>
+    <col min="5121" max="5121" width="30.875" style="5" customWidth="1"/>
+    <col min="5122" max="5123" width="20.625" style="5" customWidth="1"/>
+    <col min="5124" max="5124" width="30.875" style="5" customWidth="1"/>
+    <col min="5125" max="5126" width="20.625" style="5" customWidth="1"/>
+    <col min="5127" max="5376" width="9" style="5"/>
+    <col min="5377" max="5377" width="30.875" style="5" customWidth="1"/>
+    <col min="5378" max="5379" width="20.625" style="5" customWidth="1"/>
+    <col min="5380" max="5380" width="30.875" style="5" customWidth="1"/>
+    <col min="5381" max="5382" width="20.625" style="5" customWidth="1"/>
+    <col min="5383" max="5632" width="9" style="5"/>
+    <col min="5633" max="5633" width="30.875" style="5" customWidth="1"/>
+    <col min="5634" max="5635" width="20.625" style="5" customWidth="1"/>
+    <col min="5636" max="5636" width="30.875" style="5" customWidth="1"/>
+    <col min="5637" max="5638" width="20.625" style="5" customWidth="1"/>
+    <col min="5639" max="5888" width="9" style="5"/>
+    <col min="5889" max="5889" width="30.875" style="5" customWidth="1"/>
+    <col min="5890" max="5891" width="20.625" style="5" customWidth="1"/>
+    <col min="5892" max="5892" width="30.875" style="5" customWidth="1"/>
+    <col min="5893" max="5894" width="20.625" style="5" customWidth="1"/>
+    <col min="5895" max="6144" width="9" style="5"/>
+    <col min="6145" max="6145" width="30.875" style="5" customWidth="1"/>
+    <col min="6146" max="6147" width="20.625" style="5" customWidth="1"/>
+    <col min="6148" max="6148" width="30.875" style="5" customWidth="1"/>
+    <col min="6149" max="6150" width="20.625" style="5" customWidth="1"/>
+    <col min="6151" max="6400" width="9" style="5"/>
+    <col min="6401" max="6401" width="30.875" style="5" customWidth="1"/>
+    <col min="6402" max="6403" width="20.625" style="5" customWidth="1"/>
+    <col min="6404" max="6404" width="30.875" style="5" customWidth="1"/>
+    <col min="6405" max="6406" width="20.625" style="5" customWidth="1"/>
+    <col min="6407" max="6656" width="9" style="5"/>
+    <col min="6657" max="6657" width="30.875" style="5" customWidth="1"/>
+    <col min="6658" max="6659" width="20.625" style="5" customWidth="1"/>
+    <col min="6660" max="6660" width="30.875" style="5" customWidth="1"/>
+    <col min="6661" max="6662" width="20.625" style="5" customWidth="1"/>
+    <col min="6663" max="6912" width="9" style="5"/>
+    <col min="6913" max="6913" width="30.875" style="5" customWidth="1"/>
+    <col min="6914" max="6915" width="20.625" style="5" customWidth="1"/>
+    <col min="6916" max="6916" width="30.875" style="5" customWidth="1"/>
+    <col min="6917" max="6918" width="20.625" style="5" customWidth="1"/>
+    <col min="6919" max="7168" width="9" style="5"/>
+    <col min="7169" max="7169" width="30.875" style="5" customWidth="1"/>
+    <col min="7170" max="7171" width="20.625" style="5" customWidth="1"/>
+    <col min="7172" max="7172" width="30.875" style="5" customWidth="1"/>
+    <col min="7173" max="7174" width="20.625" style="5" customWidth="1"/>
+    <col min="7175" max="7424" width="9" style="5"/>
+    <col min="7425" max="7425" width="30.875" style="5" customWidth="1"/>
+    <col min="7426" max="7427" width="20.625" style="5" customWidth="1"/>
+    <col min="7428" max="7428" width="30.875" style="5" customWidth="1"/>
+    <col min="7429" max="7430" width="20.625" style="5" customWidth="1"/>
+    <col min="7431" max="7680" width="9" style="5"/>
+    <col min="7681" max="7681" width="30.875" style="5" customWidth="1"/>
+    <col min="7682" max="7683" width="20.625" style="5" customWidth="1"/>
+    <col min="7684" max="7684" width="30.875" style="5" customWidth="1"/>
+    <col min="7685" max="7686" width="20.625" style="5" customWidth="1"/>
+    <col min="7687" max="7936" width="9" style="5"/>
+    <col min="7937" max="7937" width="30.875" style="5" customWidth="1"/>
+    <col min="7938" max="7939" width="20.625" style="5" customWidth="1"/>
+    <col min="7940" max="7940" width="30.875" style="5" customWidth="1"/>
+    <col min="7941" max="7942" width="20.625" style="5" customWidth="1"/>
+    <col min="7943" max="8192" width="9" style="5"/>
+    <col min="8193" max="8193" width="30.875" style="5" customWidth="1"/>
+    <col min="8194" max="8195" width="20.625" style="5" customWidth="1"/>
+    <col min="8196" max="8196" width="30.875" style="5" customWidth="1"/>
+    <col min="8197" max="8198" width="20.625" style="5" customWidth="1"/>
+    <col min="8199" max="8448" width="9" style="5"/>
+    <col min="8449" max="8449" width="30.875" style="5" customWidth="1"/>
+    <col min="8450" max="8451" width="20.625" style="5" customWidth="1"/>
+    <col min="8452" max="8452" width="30.875" style="5" customWidth="1"/>
+    <col min="8453" max="8454" width="20.625" style="5" customWidth="1"/>
+    <col min="8455" max="8704" width="9" style="5"/>
+    <col min="8705" max="8705" width="30.875" style="5" customWidth="1"/>
+    <col min="8706" max="8707" width="20.625" style="5" customWidth="1"/>
+    <col min="8708" max="8708" width="30.875" style="5" customWidth="1"/>
+    <col min="8709" max="8710" width="20.625" style="5" customWidth="1"/>
+    <col min="8711" max="8960" width="9" style="5"/>
+    <col min="8961" max="8961" width="30.875" style="5" customWidth="1"/>
+    <col min="8962" max="8963" width="20.625" style="5" customWidth="1"/>
+    <col min="8964" max="8964" width="30.875" style="5" customWidth="1"/>
+    <col min="8965" max="8966" width="20.625" style="5" customWidth="1"/>
+    <col min="8967" max="9216" width="9" style="5"/>
+    <col min="9217" max="9217" width="30.875" style="5" customWidth="1"/>
+    <col min="9218" max="9219" width="20.625" style="5" customWidth="1"/>
+    <col min="9220" max="9220" width="30.875" style="5" customWidth="1"/>
+    <col min="9221" max="9222" width="20.625" style="5" customWidth="1"/>
+    <col min="9223" max="9472" width="9" style="5"/>
+    <col min="9473" max="9473" width="30.875" style="5" customWidth="1"/>
+    <col min="9474" max="9475" width="20.625" style="5" customWidth="1"/>
+    <col min="9476" max="9476" width="30.875" style="5" customWidth="1"/>
+    <col min="9477" max="9478" width="20.625" style="5" customWidth="1"/>
+    <col min="9479" max="9728" width="9" style="5"/>
+    <col min="9729" max="9729" width="30.875" style="5" customWidth="1"/>
+    <col min="9730" max="9731" width="20.625" style="5" customWidth="1"/>
+    <col min="9732" max="9732" width="30.875" style="5" customWidth="1"/>
+    <col min="9733" max="9734" width="20.625" style="5" customWidth="1"/>
+    <col min="9735" max="9984" width="9" style="5"/>
+    <col min="9985" max="9985" width="30.875" style="5" customWidth="1"/>
+    <col min="9986" max="9987" width="20.625" style="5" customWidth="1"/>
+    <col min="9988" max="9988" width="30.875" style="5" customWidth="1"/>
+    <col min="9989" max="9990" width="20.625" style="5" customWidth="1"/>
+    <col min="9991" max="10240" width="9" style="5"/>
+    <col min="10241" max="10241" width="30.875" style="5" customWidth="1"/>
+    <col min="10242" max="10243" width="20.625" style="5" customWidth="1"/>
+    <col min="10244" max="10244" width="30.875" style="5" customWidth="1"/>
+    <col min="10245" max="10246" width="20.625" style="5" customWidth="1"/>
+    <col min="10247" max="10496" width="9" style="5"/>
+    <col min="10497" max="10497" width="30.875" style="5" customWidth="1"/>
+    <col min="10498" max="10499" width="20.625" style="5" customWidth="1"/>
+    <col min="10500" max="10500" width="30.875" style="5" customWidth="1"/>
+    <col min="10501" max="10502" width="20.625" style="5" customWidth="1"/>
+    <col min="10503" max="10752" width="9" style="5"/>
+    <col min="10753" max="10753" width="30.875" style="5" customWidth="1"/>
+    <col min="10754" max="10755" width="20.625" style="5" customWidth="1"/>
+    <col min="10756" max="10756" width="30.875" style="5" customWidth="1"/>
+    <col min="10757" max="10758" width="20.625" style="5" customWidth="1"/>
+    <col min="10759" max="11008" width="9" style="5"/>
+    <col min="11009" max="11009" width="30.875" style="5" customWidth="1"/>
+    <col min="11010" max="11011" width="20.625" style="5" customWidth="1"/>
+    <col min="11012" max="11012" width="30.875" style="5" customWidth="1"/>
+    <col min="11013" max="11014" width="20.625" style="5" customWidth="1"/>
+    <col min="11015" max="11264" width="9" style="5"/>
+    <col min="11265" max="11265" width="30.875" style="5" customWidth="1"/>
+    <col min="11266" max="11267" width="20.625" style="5" customWidth="1"/>
+    <col min="11268" max="11268" width="30.875" style="5" customWidth="1"/>
+    <col min="11269" max="11270" width="20.625" style="5" customWidth="1"/>
+    <col min="11271" max="11520" width="9" style="5"/>
+    <col min="11521" max="11521" width="30.875" style="5" customWidth="1"/>
+    <col min="11522" max="11523" width="20.625" style="5" customWidth="1"/>
+    <col min="11524" max="11524" width="30.875" style="5" customWidth="1"/>
+    <col min="11525" max="11526" width="20.625" style="5" customWidth="1"/>
+    <col min="11527" max="11776" width="9" style="5"/>
+    <col min="11777" max="11777" width="30.875" style="5" customWidth="1"/>
+    <col min="11778" max="11779" width="20.625" style="5" customWidth="1"/>
+    <col min="11780" max="11780" width="30.875" style="5" customWidth="1"/>
+    <col min="11781" max="11782" width="20.625" style="5" customWidth="1"/>
+    <col min="11783" max="12032" width="9" style="5"/>
+    <col min="12033" max="12033" width="30.875" style="5" customWidth="1"/>
+    <col min="12034" max="12035" width="20.625" style="5" customWidth="1"/>
+    <col min="12036" max="12036" width="30.875" style="5" customWidth="1"/>
+    <col min="12037" max="12038" width="20.625" style="5" customWidth="1"/>
+    <col min="12039" max="12288" width="9" style="5"/>
+    <col min="12289" max="12289" width="30.875" style="5" customWidth="1"/>
+    <col min="12290" max="12291" width="20.625" style="5" customWidth="1"/>
+    <col min="12292" max="12292" width="30.875" style="5" customWidth="1"/>
+    <col min="12293" max="12294" width="20.625" style="5" customWidth="1"/>
+    <col min="12295" max="12544" width="9" style="5"/>
+    <col min="12545" max="12545" width="30.875" style="5" customWidth="1"/>
+    <col min="12546" max="12547" width="20.625" style="5" customWidth="1"/>
+    <col min="12548" max="12548" width="30.875" style="5" customWidth="1"/>
+    <col min="12549" max="12550" width="20.625" style="5" customWidth="1"/>
+    <col min="12551" max="12800" width="9" style="5"/>
+    <col min="12801" max="12801" width="30.875" style="5" customWidth="1"/>
+    <col min="12802" max="12803" width="20.625" style="5" customWidth="1"/>
+    <col min="12804" max="12804" width="30.875" style="5" customWidth="1"/>
+    <col min="12805" max="12806" width="20.625" style="5" customWidth="1"/>
+    <col min="12807" max="13056" width="9" style="5"/>
+    <col min="13057" max="13057" width="30.875" style="5" customWidth="1"/>
+    <col min="13058" max="13059" width="20.625" style="5" customWidth="1"/>
+    <col min="13060" max="13060" width="30.875" style="5" customWidth="1"/>
+    <col min="13061" max="13062" width="20.625" style="5" customWidth="1"/>
+    <col min="13063" max="13312" width="9" style="5"/>
+    <col min="13313" max="13313" width="30.875" style="5" customWidth="1"/>
+    <col min="13314" max="13315" width="20.625" style="5" customWidth="1"/>
+    <col min="13316" max="13316" width="30.875" style="5" customWidth="1"/>
+    <col min="13317" max="13318" width="20.625" style="5" customWidth="1"/>
+    <col min="13319" max="13568" width="9" style="5"/>
+    <col min="13569" max="13569" width="30.875" style="5" customWidth="1"/>
+    <col min="13570" max="13571" width="20.625" style="5" customWidth="1"/>
+    <col min="13572" max="13572" width="30.875" style="5" customWidth="1"/>
+    <col min="13573" max="13574" width="20.625" style="5" customWidth="1"/>
+    <col min="13575" max="13824" width="9" style="5"/>
+    <col min="13825" max="13825" width="30.875" style="5" customWidth="1"/>
+    <col min="13826" max="13827" width="20.625" style="5" customWidth="1"/>
+    <col min="13828" max="13828" width="30.875" style="5" customWidth="1"/>
+    <col min="13829" max="13830" width="20.625" style="5" customWidth="1"/>
+    <col min="13831" max="14080" width="9" style="5"/>
+    <col min="14081" max="14081" width="30.875" style="5" customWidth="1"/>
+    <col min="14082" max="14083" width="20.625" style="5" customWidth="1"/>
+    <col min="14084" max="14084" width="30.875" style="5" customWidth="1"/>
+    <col min="14085" max="14086" width="20.625" style="5" customWidth="1"/>
+    <col min="14087" max="14336" width="9" style="5"/>
+    <col min="14337" max="14337" width="30.875" style="5" customWidth="1"/>
+    <col min="14338" max="14339" width="20.625" style="5" customWidth="1"/>
+    <col min="14340" max="14340" width="30.875" style="5" customWidth="1"/>
+    <col min="14341" max="14342" width="20.625" style="5" customWidth="1"/>
+    <col min="14343" max="14592" width="9" style="5"/>
+    <col min="14593" max="14593" width="30.875" style="5" customWidth="1"/>
+    <col min="14594" max="14595" width="20.625" style="5" customWidth="1"/>
+    <col min="14596" max="14596" width="30.875" style="5" customWidth="1"/>
+    <col min="14597" max="14598" width="20.625" style="5" customWidth="1"/>
+    <col min="14599" max="14848" width="9" style="5"/>
+    <col min="14849" max="14849" width="30.875" style="5" customWidth="1"/>
+    <col min="14850" max="14851" width="20.625" style="5" customWidth="1"/>
+    <col min="14852" max="14852" width="30.875" style="5" customWidth="1"/>
+    <col min="14853" max="14854" width="20.625" style="5" customWidth="1"/>
+    <col min="14855" max="15104" width="9" style="5"/>
+    <col min="15105" max="15105" width="30.875" style="5" customWidth="1"/>
+    <col min="15106" max="15107" width="20.625" style="5" customWidth="1"/>
+    <col min="15108" max="15108" width="30.875" style="5" customWidth="1"/>
+    <col min="15109" max="15110" width="20.625" style="5" customWidth="1"/>
+    <col min="15111" max="15360" width="9" style="5"/>
+    <col min="15361" max="15361" width="30.875" style="5" customWidth="1"/>
+    <col min="15362" max="15363" width="20.625" style="5" customWidth="1"/>
+    <col min="15364" max="15364" width="30.875" style="5" customWidth="1"/>
+    <col min="15365" max="15366" width="20.625" style="5" customWidth="1"/>
+    <col min="15367" max="15616" width="9" style="5"/>
+    <col min="15617" max="15617" width="30.875" style="5" customWidth="1"/>
+    <col min="15618" max="15619" width="20.625" style="5" customWidth="1"/>
+    <col min="15620" max="15620" width="30.875" style="5" customWidth="1"/>
+    <col min="15621" max="15622" width="20.625" style="5" customWidth="1"/>
+    <col min="15623" max="15872" width="9" style="5"/>
+    <col min="15873" max="15873" width="30.875" style="5" customWidth="1"/>
+    <col min="15874" max="15875" width="20.625" style="5" customWidth="1"/>
+    <col min="15876" max="15876" width="30.875" style="5" customWidth="1"/>
+    <col min="15877" max="15878" width="20.625" style="5" customWidth="1"/>
+    <col min="15879" max="16128" width="9" style="5"/>
+    <col min="16129" max="16129" width="30.875" style="5" customWidth="1"/>
+    <col min="16130" max="16131" width="20.625" style="5" customWidth="1"/>
+    <col min="16132" max="16132" width="30.875" style="5" customWidth="1"/>
+    <col min="16133" max="16134" width="20.625" style="5" customWidth="1"/>
+    <col min="16135" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="5" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="12" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="14" t="s">
         <v>19</v>
       </c>
     </row>

--- a/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/finassetliabilitystatement/FinAssetLiabilityStatement.xlsx
+++ b/tams-svreport-parent/tams-svreport-chbreport/src/main/resources/tpl/finassetliabilitystatement/FinAssetLiabilityStatement.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20373"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90916A79-71C0-4FFE-AD7D-98BCBF455FC9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +27,6 @@
     <t>${reportDate}</t>
   </si>
   <si>
-    <t>${year}</t>
-  </si>
-  <si>
     <t>资产负债表</t>
   </si>
   <si>
@@ -80,13 +76,17 @@
   </si>
   <si>
     <t>${platDate}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>${year}年</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
@@ -257,9 +257,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -288,12 +285,15 @@
     <xf numFmtId="176" fontId="9" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
-    <cellStyle name="常规 3" xfId="1" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
-    <cellStyle name="超链接 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="常规 2" xfId="2"/>
+    <cellStyle name="常规 3" xfId="1"/>
+    <cellStyle name="超链接 2" xfId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -309,7 +309,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -384,23 +384,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -436,23 +419,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -628,424 +594,424 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="30.875" style="5" customWidth="1"/>
-    <col min="2" max="3" width="20.625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="30.875" style="5" customWidth="1"/>
-    <col min="5" max="6" width="20.625" style="5" customWidth="1"/>
-    <col min="7" max="256" width="9" style="5"/>
-    <col min="257" max="257" width="30.875" style="5" customWidth="1"/>
-    <col min="258" max="259" width="20.625" style="5" customWidth="1"/>
-    <col min="260" max="260" width="30.875" style="5" customWidth="1"/>
-    <col min="261" max="262" width="20.625" style="5" customWidth="1"/>
-    <col min="263" max="512" width="9" style="5"/>
-    <col min="513" max="513" width="30.875" style="5" customWidth="1"/>
-    <col min="514" max="515" width="20.625" style="5" customWidth="1"/>
-    <col min="516" max="516" width="30.875" style="5" customWidth="1"/>
-    <col min="517" max="518" width="20.625" style="5" customWidth="1"/>
-    <col min="519" max="768" width="9" style="5"/>
-    <col min="769" max="769" width="30.875" style="5" customWidth="1"/>
-    <col min="770" max="771" width="20.625" style="5" customWidth="1"/>
-    <col min="772" max="772" width="30.875" style="5" customWidth="1"/>
-    <col min="773" max="774" width="20.625" style="5" customWidth="1"/>
-    <col min="775" max="1024" width="9" style="5"/>
-    <col min="1025" max="1025" width="30.875" style="5" customWidth="1"/>
-    <col min="1026" max="1027" width="20.625" style="5" customWidth="1"/>
-    <col min="1028" max="1028" width="30.875" style="5" customWidth="1"/>
-    <col min="1029" max="1030" width="20.625" style="5" customWidth="1"/>
-    <col min="1031" max="1280" width="9" style="5"/>
-    <col min="1281" max="1281" width="30.875" style="5" customWidth="1"/>
-    <col min="1282" max="1283" width="20.625" style="5" customWidth="1"/>
-    <col min="1284" max="1284" width="30.875" style="5" customWidth="1"/>
-    <col min="1285" max="1286" width="20.625" style="5" customWidth="1"/>
-    <col min="1287" max="1536" width="9" style="5"/>
-    <col min="1537" max="1537" width="30.875" style="5" customWidth="1"/>
-    <col min="1538" max="1539" width="20.625" style="5" customWidth="1"/>
-    <col min="1540" max="1540" width="30.875" style="5" customWidth="1"/>
-    <col min="1541" max="1542" width="20.625" style="5" customWidth="1"/>
-    <col min="1543" max="1792" width="9" style="5"/>
-    <col min="1793" max="1793" width="30.875" style="5" customWidth="1"/>
-    <col min="1794" max="1795" width="20.625" style="5" customWidth="1"/>
-    <col min="1796" max="1796" width="30.875" style="5" customWidth="1"/>
-    <col min="1797" max="1798" width="20.625" style="5" customWidth="1"/>
-    <col min="1799" max="2048" width="9" style="5"/>
-    <col min="2049" max="2049" width="30.875" style="5" customWidth="1"/>
-    <col min="2050" max="2051" width="20.625" style="5" customWidth="1"/>
-    <col min="2052" max="2052" width="30.875" style="5" customWidth="1"/>
-    <col min="2053" max="2054" width="20.625" style="5" customWidth="1"/>
-    <col min="2055" max="2304" width="9" style="5"/>
-    <col min="2305" max="2305" width="30.875" style="5" customWidth="1"/>
-    <col min="2306" max="2307" width="20.625" style="5" customWidth="1"/>
-    <col min="2308" max="2308" width="30.875" style="5" customWidth="1"/>
-    <col min="2309" max="2310" width="20.625" style="5" customWidth="1"/>
-    <col min="2311" max="2560" width="9" style="5"/>
-    <col min="2561" max="2561" width="30.875" style="5" customWidth="1"/>
-    <col min="2562" max="2563" width="20.625" style="5" customWidth="1"/>
-    <col min="2564" max="2564" width="30.875" style="5" customWidth="1"/>
-    <col min="2565" max="2566" width="20.625" style="5" customWidth="1"/>
-    <col min="2567" max="2816" width="9" style="5"/>
-    <col min="2817" max="2817" width="30.875" style="5" customWidth="1"/>
-    <col min="2818" max="2819" width="20.625" style="5" customWidth="1"/>
-    <col min="2820" max="2820" width="30.875" style="5" customWidth="1"/>
-    <col min="2821" max="2822" width="20.625" style="5" customWidth="1"/>
-    <col min="2823" max="3072" width="9" style="5"/>
-    <col min="3073" max="3073" width="30.875" style="5" customWidth="1"/>
-    <col min="3074" max="3075" width="20.625" style="5" customWidth="1"/>
-    <col min="3076" max="3076" width="30.875" style="5" customWidth="1"/>
-    <col min="3077" max="3078" width="20.625" style="5" customWidth="1"/>
-    <col min="3079" max="3328" width="9" style="5"/>
-    <col min="3329" max="3329" width="30.875" style="5" customWidth="1"/>
-    <col min="3330" max="3331" width="20.625" style="5" customWidth="1"/>
-    <col min="3332" max="3332" width="30.875" style="5" customWidth="1"/>
-    <col min="3333" max="3334" width="20.625" style="5" customWidth="1"/>
-    <col min="3335" max="3584" width="9" style="5"/>
-    <col min="3585" max="3585" width="30.875" style="5" customWidth="1"/>
-    <col min="3586" max="3587" width="20.625" style="5" customWidth="1"/>
-    <col min="3588" max="3588" width="30.875" style="5" customWidth="1"/>
-    <col min="3589" max="3590" width="20.625" style="5" customWidth="1"/>
-    <col min="3591" max="3840" width="9" style="5"/>
-    <col min="3841" max="3841" width="30.875" style="5" customWidth="1"/>
-    <col min="3842" max="3843" width="20.625" style="5" customWidth="1"/>
-    <col min="3844" max="3844" width="30.875" style="5" customWidth="1"/>
-    <col min="3845" max="3846" width="20.625" style="5" customWidth="1"/>
-    <col min="3847" max="4096" width="9" style="5"/>
-    <col min="4097" max="4097" width="30.875" style="5" customWidth="1"/>
-    <col min="4098" max="4099" width="20.625" style="5" customWidth="1"/>
-    <col min="4100" max="4100" width="30.875" style="5" customWidth="1"/>
-    <col min="4101" max="4102" width="20.625" style="5" customWidth="1"/>
-    <col min="4103" max="4352" width="9" style="5"/>
-    <col min="4353" max="4353" width="30.875" style="5" customWidth="1"/>
-    <col min="4354" max="4355" width="20.625" style="5" customWidth="1"/>
-    <col min="4356" max="4356" width="30.875" style="5" customWidth="1"/>
-    <col min="4357" max="4358" width="20.625" style="5" customWidth="1"/>
-    <col min="4359" max="4608" width="9" style="5"/>
-    <col min="4609" max="4609" width="30.875" style="5" customWidth="1"/>
-    <col min="4610" max="4611" width="20.625" style="5" customWidth="1"/>
-    <col min="4612" max="4612" width="30.875" style="5" customWidth="1"/>
-    <col min="4613" max="4614" width="20.625" style="5" customWidth="1"/>
-    <col min="4615" max="4864" width="9" style="5"/>
-    <col min="4865" max="4865" width="30.875" style="5" customWidth="1"/>
-    <col min="4866" max="4867" width="20.625" style="5" customWidth="1"/>
-    <col min="4868" max="4868" width="30.875" style="5" customWidth="1"/>
-    <col min="4869" max="4870" width="20.625" style="5" customWidth="1"/>
-    <col min="4871" max="5120" width="9" style="5"/>
-    <col min="5121" max="5121" width="30.875" style="5" customWidth="1"/>
-    <col min="5122" max="5123" width="20.625" style="5" customWidth="1"/>
-    <col min="5124" max="5124" width="30.875" style="5" customWidth="1"/>
-    <col min="5125" max="5126" width="20.625" style="5" customWidth="1"/>
-    <col min="5127" max="5376" width="9" style="5"/>
-    <col min="5377" max="5377" width="30.875" style="5" customWidth="1"/>
-    <col min="5378" max="5379" width="20.625" style="5" customWidth="1"/>
-    <col min="5380" max="5380" width="30.875" style="5" customWidth="1"/>
-    <col min="5381" max="5382" width="20.625" style="5" customWidth="1"/>
-    <col min="5383" max="5632" width="9" style="5"/>
-    <col min="5633" max="5633" width="30.875" style="5" customWidth="1"/>
-    <col min="5634" max="5635" width="20.625" style="5" customWidth="1"/>
-    <col min="5636" max="5636" width="30.875" style="5" customWidth="1"/>
-    <col min="5637" max="5638" width="20.625" style="5" customWidth="1"/>
-    <col min="5639" max="5888" width="9" style="5"/>
-    <col min="5889" max="5889" width="30.875" style="5" customWidth="1"/>
-    <col min="5890" max="5891" width="20.625" style="5" customWidth="1"/>
-    <col min="5892" max="5892" width="30.875" style="5" customWidth="1"/>
-    <col min="5893" max="5894" width="20.625" style="5" customWidth="1"/>
-    <col min="5895" max="6144" width="9" style="5"/>
-    <col min="6145" max="6145" width="30.875" style="5" customWidth="1"/>
-    <col min="6146" max="6147" width="20.625" style="5" customWidth="1"/>
-    <col min="6148" max="6148" width="30.875" style="5" customWidth="1"/>
-    <col min="6149" max="6150" width="20.625" style="5" customWidth="1"/>
-    <col min="6151" max="6400" width="9" style="5"/>
-    <col min="6401" max="6401" width="30.875" style="5" customWidth="1"/>
-    <col min="6402" max="6403" width="20.625" style="5" customWidth="1"/>
-    <col min="6404" max="6404" width="30.875" style="5" customWidth="1"/>
-    <col min="6405" max="6406" width="20.625" style="5" customWidth="1"/>
-    <col min="6407" max="6656" width="9" style="5"/>
-    <col min="6657" max="6657" width="30.875" style="5" customWidth="1"/>
-    <col min="6658" max="6659" width="20.625" style="5" customWidth="1"/>
-    <col min="6660" max="6660" width="30.875" style="5" customWidth="1"/>
-    <col min="6661" max="6662" width="20.625" style="5" customWidth="1"/>
-    <col min="6663" max="6912" width="9" style="5"/>
-    <col min="6913" max="6913" width="30.875" style="5" customWidth="1"/>
-    <col min="6914" max="6915" width="20.625" style="5" customWidth="1"/>
-    <col min="6916" max="6916" width="30.875" style="5" customWidth="1"/>
-    <col min="6917" max="6918" width="20.625" style="5" customWidth="1"/>
-    <col min="6919" max="7168" width="9" style="5"/>
-    <col min="7169" max="7169" width="30.875" style="5" customWidth="1"/>
-    <col min="7170" max="7171" width="20.625" style="5" customWidth="1"/>
-    <col min="7172" max="7172" width="30.875" style="5" customWidth="1"/>
-    <col min="7173" max="7174" width="20.625" style="5" customWidth="1"/>
-    <col min="7175" max="7424" width="9" style="5"/>
-    <col min="7425" max="7425" width="30.875" style="5" customWidth="1"/>
-    <col min="7426" max="7427" width="20.625" style="5" customWidth="1"/>
-    <col min="7428" max="7428" width="30.875" style="5" customWidth="1"/>
-    <col min="7429" max="7430" width="20.625" style="5" customWidth="1"/>
-    <col min="7431" max="7680" width="9" style="5"/>
-    <col min="7681" max="7681" width="30.875" style="5" customWidth="1"/>
-    <col min="7682" max="7683" width="20.625" style="5" customWidth="1"/>
-    <col min="7684" max="7684" width="30.875" style="5" customWidth="1"/>
-    <col min="7685" max="7686" width="20.625" style="5" customWidth="1"/>
-    <col min="7687" max="7936" width="9" style="5"/>
-    <col min="7937" max="7937" width="30.875" style="5" customWidth="1"/>
-    <col min="7938" max="7939" width="20.625" style="5" customWidth="1"/>
-    <col min="7940" max="7940" width="30.875" style="5" customWidth="1"/>
-    <col min="7941" max="7942" width="20.625" style="5" customWidth="1"/>
-    <col min="7943" max="8192" width="9" style="5"/>
-    <col min="8193" max="8193" width="30.875" style="5" customWidth="1"/>
-    <col min="8194" max="8195" width="20.625" style="5" customWidth="1"/>
-    <col min="8196" max="8196" width="30.875" style="5" customWidth="1"/>
-    <col min="8197" max="8198" width="20.625" style="5" customWidth="1"/>
-    <col min="8199" max="8448" width="9" style="5"/>
-    <col min="8449" max="8449" width="30.875" style="5" customWidth="1"/>
-    <col min="8450" max="8451" width="20.625" style="5" customWidth="1"/>
-    <col min="8452" max="8452" width="30.875" style="5" customWidth="1"/>
-    <col min="8453" max="8454" width="20.625" style="5" customWidth="1"/>
-    <col min="8455" max="8704" width="9" style="5"/>
-    <col min="8705" max="8705" width="30.875" style="5" customWidth="1"/>
-    <col min="8706" max="8707" width="20.625" style="5" customWidth="1"/>
-    <col min="8708" max="8708" width="30.875" style="5" customWidth="1"/>
-    <col min="8709" max="8710" width="20.625" style="5" customWidth="1"/>
-    <col min="8711" max="8960" width="9" style="5"/>
-    <col min="8961" max="8961" width="30.875" style="5" customWidth="1"/>
-    <col min="8962" max="8963" width="20.625" style="5" customWidth="1"/>
-    <col min="8964" max="8964" width="30.875" style="5" customWidth="1"/>
-    <col min="8965" max="8966" width="20.625" style="5" customWidth="1"/>
-    <col min="8967" max="9216" width="9" style="5"/>
-    <col min="9217" max="9217" width="30.875" style="5" customWidth="1"/>
-    <col min="9218" max="9219" width="20.625" style="5" customWidth="1"/>
-    <col min="9220" max="9220" width="30.875" style="5" customWidth="1"/>
-    <col min="9221" max="9222" width="20.625" style="5" customWidth="1"/>
-    <col min="9223" max="9472" width="9" style="5"/>
-    <col min="9473" max="9473" width="30.875" style="5" customWidth="1"/>
-    <col min="9474" max="9475" width="20.625" style="5" customWidth="1"/>
-    <col min="9476" max="9476" width="30.875" style="5" customWidth="1"/>
-    <col min="9477" max="9478" width="20.625" style="5" customWidth="1"/>
-    <col min="9479" max="9728" width="9" style="5"/>
-    <col min="9729" max="9729" width="30.875" style="5" customWidth="1"/>
-    <col min="9730" max="9731" width="20.625" style="5" customWidth="1"/>
-    <col min="9732" max="9732" width="30.875" style="5" customWidth="1"/>
-    <col min="9733" max="9734" width="20.625" style="5" customWidth="1"/>
-    <col min="9735" max="9984" width="9" style="5"/>
-    <col min="9985" max="9985" width="30.875" style="5" customWidth="1"/>
-    <col min="9986" max="9987" width="20.625" style="5" customWidth="1"/>
-    <col min="9988" max="9988" width="30.875" style="5" customWidth="1"/>
-    <col min="9989" max="9990" width="20.625" style="5" customWidth="1"/>
-    <col min="9991" max="10240" width="9" style="5"/>
-    <col min="10241" max="10241" width="30.875" style="5" customWidth="1"/>
-    <col min="10242" max="10243" width="20.625" style="5" customWidth="1"/>
-    <col min="10244" max="10244" width="30.875" style="5" customWidth="1"/>
-    <col min="10245" max="10246" width="20.625" style="5" customWidth="1"/>
-    <col min="10247" max="10496" width="9" style="5"/>
-    <col min="10497" max="10497" width="30.875" style="5" customWidth="1"/>
-    <col min="10498" max="10499" width="20.625" style="5" customWidth="1"/>
-    <col min="10500" max="10500" width="30.875" style="5" customWidth="1"/>
-    <col min="10501" max="10502" width="20.625" style="5" customWidth="1"/>
-    <col min="10503" max="10752" width="9" style="5"/>
-    <col min="10753" max="10753" width="30.875" style="5" customWidth="1"/>
-    <col min="10754" max="10755" width="20.625" style="5" customWidth="1"/>
-    <col min="10756" max="10756" width="30.875" style="5" customWidth="1"/>
-    <col min="10757" max="10758" width="20.625" style="5" customWidth="1"/>
-    <col min="10759" max="11008" width="9" style="5"/>
-    <col min="11009" max="11009" width="30.875" style="5" customWidth="1"/>
-    <col min="11010" max="11011" width="20.625" style="5" customWidth="1"/>
-    <col min="11012" max="11012" width="30.875" style="5" customWidth="1"/>
-    <col min="11013" max="11014" width="20.625" style="5" customWidth="1"/>
-    <col min="11015" max="11264" width="9" style="5"/>
-    <col min="11265" max="11265" width="30.875" style="5" customWidth="1"/>
-    <col min="11266" max="11267" width="20.625" style="5" customWidth="1"/>
-    <col min="11268" max="11268" width="30.875" style="5" customWidth="1"/>
-    <col min="11269" max="11270" width="20.625" style="5" customWidth="1"/>
-    <col min="11271" max="11520" width="9" style="5"/>
-    <col min="11521" max="11521" width="30.875" style="5" customWidth="1"/>
-    <col min="11522" max="11523" width="20.625" style="5" customWidth="1"/>
-    <col min="11524" max="11524" width="30.875" style="5" customWidth="1"/>
-    <col min="11525" max="11526" width="20.625" style="5" customWidth="1"/>
-    <col min="11527" max="11776" width="9" style="5"/>
-    <col min="11777" max="11777" width="30.875" style="5" customWidth="1"/>
-    <col min="11778" max="11779" width="20.625" style="5" customWidth="1"/>
-    <col min="11780" max="11780" width="30.875" style="5" customWidth="1"/>
-    <col min="11781" max="11782" width="20.625" style="5" customWidth="1"/>
-    <col min="11783" max="12032" width="9" style="5"/>
-    <col min="12033" max="12033" width="30.875" style="5" customWidth="1"/>
-    <col min="12034" max="12035" width="20.625" style="5" customWidth="1"/>
-    <col min="12036" max="12036" width="30.875" style="5" customWidth="1"/>
-    <col min="12037" max="12038" width="20.625" style="5" customWidth="1"/>
-    <col min="12039" max="12288" width="9" style="5"/>
-    <col min="12289" max="12289" width="30.875" style="5" customWidth="1"/>
-    <col min="12290" max="12291" width="20.625" style="5" customWidth="1"/>
-    <col min="12292" max="12292" width="30.875" style="5" customWidth="1"/>
-    <col min="12293" max="12294" width="20.625" style="5" customWidth="1"/>
-    <col min="12295" max="12544" width="9" style="5"/>
-    <col min="12545" max="12545" width="30.875" style="5" customWidth="1"/>
-    <col min="12546" max="12547" width="20.625" style="5" customWidth="1"/>
-    <col min="12548" max="12548" width="30.875" style="5" customWidth="1"/>
-    <col min="12549" max="12550" width="20.625" style="5" customWidth="1"/>
-    <col min="12551" max="12800" width="9" style="5"/>
-    <col min="12801" max="12801" width="30.875" style="5" customWidth="1"/>
-    <col min="12802" max="12803" width="20.625" style="5" customWidth="1"/>
-    <col min="12804" max="12804" width="30.875" style="5" customWidth="1"/>
-    <col min="12805" max="12806" width="20.625" style="5" customWidth="1"/>
-    <col min="12807" max="13056" width="9" style="5"/>
-    <col min="13057" max="13057" width="30.875" style="5" customWidth="1"/>
-    <col min="13058" max="13059" width="20.625" style="5" customWidth="1"/>
-    <col min="13060" max="13060" width="30.875" style="5" customWidth="1"/>
-    <col min="13061" max="13062" width="20.625" style="5" customWidth="1"/>
-    <col min="13063" max="13312" width="9" style="5"/>
-    <col min="13313" max="13313" width="30.875" style="5" customWidth="1"/>
-    <col min="13314" max="13315" width="20.625" style="5" customWidth="1"/>
-    <col min="13316" max="13316" width="30.875" style="5" customWidth="1"/>
-    <col min="13317" max="13318" width="20.625" style="5" customWidth="1"/>
-    <col min="13319" max="13568" width="9" style="5"/>
-    <col min="13569" max="13569" width="30.875" style="5" customWidth="1"/>
-    <col min="13570" max="13571" width="20.625" style="5" customWidth="1"/>
-    <col min="13572" max="13572" width="30.875" style="5" customWidth="1"/>
-    <col min="13573" max="13574" width="20.625" style="5" customWidth="1"/>
-    <col min="13575" max="13824" width="9" style="5"/>
-    <col min="13825" max="13825" width="30.875" style="5" customWidth="1"/>
-    <col min="13826" max="13827" width="20.625" style="5" customWidth="1"/>
-    <col min="13828" max="13828" width="30.875" style="5" customWidth="1"/>
-    <col min="13829" max="13830" width="20.625" style="5" customWidth="1"/>
-    <col min="13831" max="14080" width="9" style="5"/>
-    <col min="14081" max="14081" width="30.875" style="5" customWidth="1"/>
-    <col min="14082" max="14083" width="20.625" style="5" customWidth="1"/>
-    <col min="14084" max="14084" width="30.875" style="5" customWidth="1"/>
-    <col min="14085" max="14086" width="20.625" style="5" customWidth="1"/>
-    <col min="14087" max="14336" width="9" style="5"/>
-    <col min="14337" max="14337" width="30.875" style="5" customWidth="1"/>
-    <col min="14338" max="14339" width="20.625" style="5" customWidth="1"/>
-    <col min="14340" max="14340" width="30.875" style="5" customWidth="1"/>
-    <col min="14341" max="14342" width="20.625" style="5" customWidth="1"/>
-    <col min="14343" max="14592" width="9" style="5"/>
-    <col min="14593" max="14593" width="30.875" style="5" customWidth="1"/>
-    <col min="14594" max="14595" width="20.625" style="5" customWidth="1"/>
-    <col min="14596" max="14596" width="30.875" style="5" customWidth="1"/>
-    <col min="14597" max="14598" width="20.625" style="5" customWidth="1"/>
-    <col min="14599" max="14848" width="9" style="5"/>
-    <col min="14849" max="14849" width="30.875" style="5" customWidth="1"/>
-    <col min="14850" max="14851" width="20.625" style="5" customWidth="1"/>
-    <col min="14852" max="14852" width="30.875" style="5" customWidth="1"/>
-    <col min="14853" max="14854" width="20.625" style="5" customWidth="1"/>
-    <col min="14855" max="15104" width="9" style="5"/>
-    <col min="15105" max="15105" width="30.875" style="5" customWidth="1"/>
-    <col min="15106" max="15107" width="20.625" style="5" customWidth="1"/>
-    <col min="15108" max="15108" width="30.875" style="5" customWidth="1"/>
-    <col min="15109" max="15110" width="20.625" style="5" customWidth="1"/>
-    <col min="15111" max="15360" width="9" style="5"/>
-    <col min="15361" max="15361" width="30.875" style="5" customWidth="1"/>
-    <col min="15362" max="15363" width="20.625" style="5" customWidth="1"/>
-    <col min="15364" max="15364" width="30.875" style="5" customWidth="1"/>
-    <col min="15365" max="15366" width="20.625" style="5" customWidth="1"/>
-    <col min="15367" max="15616" width="9" style="5"/>
-    <col min="15617" max="15617" width="30.875" style="5" customWidth="1"/>
-    <col min="15618" max="15619" width="20.625" style="5" customWidth="1"/>
-    <col min="15620" max="15620" width="30.875" style="5" customWidth="1"/>
-    <col min="15621" max="15622" width="20.625" style="5" customWidth="1"/>
-    <col min="15623" max="15872" width="9" style="5"/>
-    <col min="15873" max="15873" width="30.875" style="5" customWidth="1"/>
-    <col min="15874" max="15875" width="20.625" style="5" customWidth="1"/>
-    <col min="15876" max="15876" width="30.875" style="5" customWidth="1"/>
-    <col min="15877" max="15878" width="20.625" style="5" customWidth="1"/>
-    <col min="15879" max="16128" width="9" style="5"/>
-    <col min="16129" max="16129" width="30.875" style="5" customWidth="1"/>
-    <col min="16130" max="16131" width="20.625" style="5" customWidth="1"/>
-    <col min="16132" max="16132" width="30.875" style="5" customWidth="1"/>
-    <col min="16133" max="16134" width="20.625" style="5" customWidth="1"/>
-    <col min="16135" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="30.875" style="4" customWidth="1"/>
+    <col min="2" max="3" width="20.625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="30.875" style="4" customWidth="1"/>
+    <col min="5" max="6" width="20.625" style="4" customWidth="1"/>
+    <col min="7" max="256" width="9" style="4"/>
+    <col min="257" max="257" width="30.875" style="4" customWidth="1"/>
+    <col min="258" max="259" width="20.625" style="4" customWidth="1"/>
+    <col min="260" max="260" width="30.875" style="4" customWidth="1"/>
+    <col min="261" max="262" width="20.625" style="4" customWidth="1"/>
+    <col min="263" max="512" width="9" style="4"/>
+    <col min="513" max="513" width="30.875" style="4" customWidth="1"/>
+    <col min="514" max="515" width="20.625" style="4" customWidth="1"/>
+    <col min="516" max="516" width="30.875" style="4" customWidth="1"/>
+    <col min="517" max="518" width="20.625" style="4" customWidth="1"/>
+    <col min="519" max="768" width="9" style="4"/>
+    <col min="769" max="769" width="30.875" style="4" customWidth="1"/>
+    <col min="770" max="771" width="20.625" style="4" customWidth="1"/>
+    <col min="772" max="772" width="30.875" style="4" customWidth="1"/>
+    <col min="773" max="774" width="20.625" style="4" customWidth="1"/>
+    <col min="775" max="1024" width="9" style="4"/>
+    <col min="1025" max="1025" width="30.875" style="4" customWidth="1"/>
+    <col min="1026" max="1027" width="20.625" style="4" customWidth="1"/>
+    <col min="1028" max="1028" width="30.875" style="4" customWidth="1"/>
+    <col min="1029" max="1030" width="20.625" style="4" customWidth="1"/>
+    <col min="1031" max="1280" width="9" style="4"/>
+    <col min="1281" max="1281" width="30.875" style="4" customWidth="1"/>
+    <col min="1282" max="1283" width="20.625" style="4" customWidth="1"/>
+    <col min="1284" max="1284" width="30.875" style="4" customWidth="1"/>
+    <col min="1285" max="1286" width="20.625" style="4" customWidth="1"/>
+    <col min="1287" max="1536" width="9" style="4"/>
+    <col min="1537" max="1537" width="30.875" style="4" customWidth="1"/>
+    <col min="1538" max="1539" width="20.625" style="4" customWidth="1"/>
+    <col min="1540" max="1540" width="30.875" style="4" customWidth="1"/>
+    <col min="1541" max="1542" width="20.625" style="4" customWidth="1"/>
+    <col min="1543" max="1792" width="9" style="4"/>
+    <col min="1793" max="1793" width="30.875" style="4" customWidth="1"/>
+    <col min="1794" max="1795" width="20.625" style="4" customWidth="1"/>
+    <col min="1796" max="1796" width="30.875" style="4" customWidth="1"/>
+    <col min="1797" max="1798" width="20.625" style="4" customWidth="1"/>
+    <col min="1799" max="2048" width="9" style="4"/>
+    <col min="2049" max="2049" width="30.875" style="4" customWidth="1"/>
+    <col min="2050" max="2051" width="20.625" style="4" customWidth="1"/>
+    <col min="2052" max="2052" width="30.875" style="4" customWidth="1"/>
+    <col min="2053" max="2054" width="20.625" style="4" customWidth="1"/>
+    <col min="2055" max="2304" width="9" style="4"/>
+    <col min="2305" max="2305" width="30.875" style="4" customWidth="1"/>
+    <col min="2306" max="2307" width="20.625" style="4" customWidth="1"/>
+    <col min="2308" max="2308" width="30.875" style="4" customWidth="1"/>
+    <col min="2309" max="2310" width="20.625" style="4" customWidth="1"/>
+    <col min="2311" max="2560" width="9" style="4"/>
+    <col min="2561" max="2561" width="30.875" style="4" customWidth="1"/>
+    <col min="2562" max="2563" width="20.625" style="4" customWidth="1"/>
+    <col min="2564" max="2564" width="30.875" style="4" customWidth="1"/>
+    <col min="2565" max="2566" width="20.625" style="4" customWidth="1"/>
+    <col min="2567" max="2816" width="9" style="4"/>
+    <col min="2817" max="2817" width="30.875" style="4" customWidth="1"/>
+    <col min="2818" max="2819" width="20.625" style="4" customWidth="1"/>
+    <col min="2820" max="2820" width="30.875" style="4" customWidth="1"/>
+    <col min="2821" max="2822" width="20.625" style="4" customWidth="1"/>
+    <col min="2823" max="3072" width="9" style="4"/>
+    <col min="3073" max="3073" width="30.875" style="4" customWidth="1"/>
+    <col min="3074" max="3075" width="20.625" style="4" customWidth="1"/>
+    <col min="3076" max="3076" width="30.875" style="4" customWidth="1"/>
+    <col min="3077" max="3078" width="20.625" style="4" customWidth="1"/>
+    <col min="3079" max="3328" width="9" style="4"/>
+    <col min="3329" max="3329" width="30.875" style="4" customWidth="1"/>
+    <col min="3330" max="3331" width="20.625" style="4" customWidth="1"/>
+    <col min="3332" max="3332" width="30.875" style="4" customWidth="1"/>
+    <col min="3333" max="3334" width="20.625" style="4" customWidth="1"/>
+    <col min="3335" max="3584" width="9" style="4"/>
+    <col min="3585" max="3585" width="30.875" style="4" customWidth="1"/>
+    <col min="3586" max="3587" width="20.625" style="4" customWidth="1"/>
+    <col min="3588" max="3588" width="30.875" style="4" customWidth="1"/>
+    <col min="3589" max="3590" width="20.625" style="4" customWidth="1"/>
+    <col min="3591" max="3840" width="9" style="4"/>
+    <col min="3841" max="3841" width="30.875" style="4" customWidth="1"/>
+    <col min="3842" max="3843" width="20.625" style="4" customWidth="1"/>
+    <col min="3844" max="3844" width="30.875" style="4" customWidth="1"/>
+    <col min="3845" max="3846" width="20.625" style="4" customWidth="1"/>
+    <col min="3847" max="4096" width="9" style="4"/>
+    <col min="4097" max="4097" width="30.875" style="4" customWidth="1"/>
+    <col min="4098" max="4099" width="20.625" style="4" customWidth="1"/>
+    <col min="4100" max="4100" width="30.875" style="4" customWidth="1"/>
+    <col min="4101" max="4102" width="20.625" style="4" customWidth="1"/>
+    <col min="4103" max="4352" width="9" style="4"/>
+    <col min="4353" max="4353" width="30.875" style="4" customWidth="1"/>
+    <col min="4354" max="4355" width="20.625" style="4" customWidth="1"/>
+    <col min="4356" max="4356" width="30.875" style="4" customWidth="1"/>
+    <col min="4357" max="4358" width="20.625" style="4" customWidth="1"/>
+    <col min="4359" max="4608" width="9" style="4"/>
+    <col min="4609" max="4609" width="30.875" style="4" customWidth="1"/>
+    <col min="4610" max="4611" width="20.625" style="4" customWidth="1"/>
+    <col min="4612" max="4612" width="30.875" style="4" customWidth="1"/>
+    <col min="4613" max="4614" width="20.625" style="4" customWidth="1"/>
+    <col min="4615" max="4864" width="9" style="4"/>
+    <col min="4865" max="4865" width="30.875" style="4" customWidth="1"/>
+    <col min="4866" max="4867" width="20.625" style="4" customWidth="1"/>
+    <col min="4868" max="4868" width="30.875" style="4" customWidth="1"/>
+    <col min="4869" max="4870" width="20.625" style="4" customWidth="1"/>
+    <col min="4871" max="5120" width="9" style="4"/>
+    <col min="5121" max="5121" width="30.875" style="4" customWidth="1"/>
+    <col min="5122" max="5123" width="20.625" style="4" customWidth="1"/>
+    <col min="5124" max="5124" width="30.875" style="4" customWidth="1"/>
+    <col min="5125" max="5126" width="20.625" style="4" customWidth="1"/>
+    <col min="5127" max="5376" width="9" style="4"/>
+    <col min="5377" max="5377" width="30.875" style="4" customWidth="1"/>
+    <col min="5378" max="5379" width="20.625" style="4" customWidth="1"/>
+    <col min="5380" max="5380" width="30.875" style="4" customWidth="1"/>
+    <col min="5381" max="5382" width="20.625" style="4" customWidth="1"/>
+    <col min="5383" max="5632" width="9" style="4"/>
+    <col min="5633" max="5633" width="30.875" style="4" customWidth="1"/>
+    <col min="5634" max="5635" width="20.625" style="4" customWidth="1"/>
+    <col min="5636" max="5636" width="30.875" style="4" customWidth="1"/>
+    <col min="5637" max="5638" width="20.625" style="4" customWidth="1"/>
+    <col min="5639" max="5888" width="9" style="4"/>
+    <col min="5889" max="5889" width="30.875" style="4" customWidth="1"/>
+    <col min="5890" max="5891" width="20.625" style="4" customWidth="1"/>
+    <col min="5892" max="5892" width="30.875" style="4" customWidth="1"/>
+    <col min="5893" max="5894" width="20.625" style="4" customWidth="1"/>
+    <col min="5895" max="6144" width="9" style="4"/>
+    <col min="6145" max="6145" width="30.875" style="4" customWidth="1"/>
+    <col min="6146" max="6147" width="20.625" style="4" customWidth="1"/>
+    <col min="6148" max="6148" width="30.875" style="4" customWidth="1"/>
+    <col min="6149" max="6150" width="20.625" style="4" customWidth="1"/>
+    <col min="6151" max="6400" width="9" style="4"/>
+    <col min="6401" max="6401" width="30.875" style="4" customWidth="1"/>
+    <col min="6402" max="6403" width="20.625" style="4" customWidth="1"/>
+    <col min="6404" max="6404" width="30.875" style="4" customWidth="1"/>
+    <col min="6405" max="6406" width="20.625" style="4" customWidth="1"/>
+    <col min="6407" max="6656" width="9" style="4"/>
+    <col min="6657" max="6657" width="30.875" style="4" customWidth="1"/>
+    <col min="6658" max="6659" width="20.625" style="4" customWidth="1"/>
+    <col min="6660" max="6660" width="30.875" style="4" customWidth="1"/>
+    <col min="6661" max="6662" width="20.625" style="4" customWidth="1"/>
+    <col min="6663" max="6912" width="9" style="4"/>
+    <col min="6913" max="6913" width="30.875" style="4" customWidth="1"/>
+    <col min="6914" max="6915" width="20.625" style="4" customWidth="1"/>
+    <col min="6916" max="6916" width="30.875" style="4" customWidth="1"/>
+    <col min="6917" max="6918" width="20.625" style="4" customWidth="1"/>
+    <col min="6919" max="7168" width="9" style="4"/>
+    <col min="7169" max="7169" width="30.875" style="4" customWidth="1"/>
+    <col min="7170" max="7171" width="20.625" style="4" customWidth="1"/>
+    <col min="7172" max="7172" width="30.875" style="4" customWidth="1"/>
+    <col min="7173" max="7174" width="20.625" style="4" customWidth="1"/>
+    <col min="7175" max="7424" width="9" style="4"/>
+    <col min="7425" max="7425" width="30.875" style="4" customWidth="1"/>
+    <col min="7426" max="7427" width="20.625" style="4" customWidth="1"/>
+    <col min="7428" max="7428" width="30.875" style="4" customWidth="1"/>
+    <col min="7429" max="7430" width="20.625" style="4" customWidth="1"/>
+    <col min="7431" max="7680" width="9" style="4"/>
+    <col min="7681" max="7681" width="30.875" style="4" customWidth="1"/>
+    <col min="7682" max="7683" width="20.625" style="4" customWidth="1"/>
+    <col min="7684" max="7684" width="30.875" style="4" customWidth="1"/>
+    <col min="7685" max="7686" width="20.625" style="4" customWidth="1"/>
+    <col min="7687" max="7936" width="9" style="4"/>
+    <col min="7937" max="7937" width="30.875" style="4" customWidth="1"/>
+    <col min="7938" max="7939" width="20.625" style="4" customWidth="1"/>
+    <col min="7940" max="7940" width="30.875" style="4" customWidth="1"/>
+    <col min="7941" max="7942" width="20.625" style="4" customWidth="1"/>
+    <col min="7943" max="8192" width="9" style="4"/>
+    <col min="8193" max="8193" width="30.875" style="4" customWidth="1"/>
+    <col min="8194" max="8195" width="20.625" style="4" customWidth="1"/>
+    <col min="8196" max="8196" width="30.875" style="4" customWidth="1"/>
+    <col min="8197" max="8198" width="20.625" style="4" customWidth="1"/>
+    <col min="8199" max="8448" width="9" style="4"/>
+    <col min="8449" max="8449" width="30.875" style="4" customWidth="1"/>
+    <col min="8450" max="8451" width="20.625" style="4" customWidth="1"/>
+    <col min="8452" max="8452" width="30.875" style="4" customWidth="1"/>
+    <col min="8453" max="8454" width="20.625" style="4" customWidth="1"/>
+    <col min="8455" max="8704" width="9" style="4"/>
+    <col min="8705" max="8705" width="30.875" style="4" customWidth="1"/>
+    <col min="8706" max="8707" width="20.625" style="4" customWidth="1"/>
+    <col min="8708" max="8708" width="30.875" style="4" customWidth="1"/>
+    <col min="8709" max="8710" width="20.625" style="4" customWidth="1"/>
+    <col min="8711" max="8960" width="9" style="4"/>
+    <col min="8961" max="8961" width="30.875" style="4" customWidth="1"/>
+    <col min="8962" max="8963" width="20.625" style="4" customWidth="1"/>
+    <col min="8964" max="8964" width="30.875" style="4" customWidth="1"/>
+    <col min="8965" max="8966" width="20.625" style="4" customWidth="1"/>
+    <col min="8967" max="9216" width="9" style="4"/>
+    <col min="9217" max="9217" width="30.875" style="4" customWidth="1"/>
+    <col min="9218" max="9219" width="20.625" style="4" customWidth="1"/>
+    <col min="9220" max="9220" width="30.875" style="4" customWidth="1"/>
+    <col min="9221" max="9222" width="20.625" style="4" customWidth="1"/>
+    <col min="9223" max="9472" width="9" style="4"/>
+    <col min="9473" max="9473" width="30.875" style="4" customWidth="1"/>
+    <col min="9474" max="9475" width="20.625" style="4" customWidth="1"/>
+    <col min="9476" max="9476" width="30.875" style="4" customWidth="1"/>
+    <col min="9477" max="9478" width="20.625" style="4" customWidth="1"/>
+    <col min="9479" max="9728" width="9" style="4"/>
+    <col min="9729" max="9729" width="30.875" style="4" customWidth="1"/>
+    <col min="9730" max="9731" width="20.625" style="4" customWidth="1"/>
+    <col min="9732" max="9732" width="30.875" style="4" customWidth="1"/>
+    <col min="9733" max="9734" width="20.625" style="4" customWidth="1"/>
+    <col min="9735" max="9984" width="9" style="4"/>
+    <col min="9985" max="9985" width="30.875" style="4" customWidth="1"/>
+    <col min="9986" max="9987" width="20.625" style="4" customWidth="1"/>
+    <col min="9988" max="9988" width="30.875" style="4" customWidth="1"/>
+    <col min="9989" max="9990" width="20.625" style="4" customWidth="1"/>
+    <col min="9991" max="10240" width="9" style="4"/>
+    <col min="10241" max="10241" width="30.875" style="4" customWidth="1"/>
+    <col min="10242" max="10243" width="20.625" style="4" customWidth="1"/>
+    <col min="10244" max="10244" width="30.875" style="4" customWidth="1"/>
+    <col min="10245" max="10246" width="20.625" style="4" customWidth="1"/>
+    <col min="10247" max="10496" width="9" style="4"/>
+    <col min="10497" max="10497" width="30.875" style="4" customWidth="1"/>
+    <col min="10498" max="10499" width="20.625" style="4" customWidth="1"/>
+    <col min="10500" max="10500" width="30.875" style="4" customWidth="1"/>
+    <col min="10501" max="10502" width="20.625" style="4" customWidth="1"/>
+    <col min="10503" max="10752" width="9" style="4"/>
+    <col min="10753" max="10753" width="30.875" style="4" customWidth="1"/>
+    <col min="10754" max="10755" width="20.625" style="4" customWidth="1"/>
+    <col min="10756" max="10756" width="30.875" style="4" customWidth="1"/>
+    <col min="10757" max="10758" width="20.625" style="4" customWidth="1"/>
+    <col min="10759" max="11008" width="9" style="4"/>
+    <col min="11009" max="11009" width="30.875" style="4" customWidth="1"/>
+    <col min="11010" max="11011" width="20.625" style="4" customWidth="1"/>
+    <col min="11012" max="11012" width="30.875" style="4" customWidth="1"/>
+    <col min="11013" max="11014" width="20.625" style="4" customWidth="1"/>
+    <col min="11015" max="11264" width="9" style="4"/>
+    <col min="11265" max="11265" width="30.875" style="4" customWidth="1"/>
+    <col min="11266" max="11267" width="20.625" style="4" customWidth="1"/>
+    <col min="11268" max="11268" width="30.875" style="4" customWidth="1"/>
+    <col min="11269" max="11270" width="20.625" style="4" customWidth="1"/>
+    <col min="11271" max="11520" width="9" style="4"/>
+    <col min="11521" max="11521" width="30.875" style="4" customWidth="1"/>
+    <col min="11522" max="11523" width="20.625" style="4" customWidth="1"/>
+    <col min="11524" max="11524" width="30.875" style="4" customWidth="1"/>
+    <col min="11525" max="11526" width="20.625" style="4" customWidth="1"/>
+    <col min="11527" max="11776" width="9" style="4"/>
+    <col min="11777" max="11777" width="30.875" style="4" customWidth="1"/>
+    <col min="11778" max="11779" width="20.625" style="4" customWidth="1"/>
+    <col min="11780" max="11780" width="30.875" style="4" customWidth="1"/>
+    <col min="11781" max="11782" width="20.625" style="4" customWidth="1"/>
+    <col min="11783" max="12032" width="9" style="4"/>
+    <col min="12033" max="12033" width="30.875" style="4" customWidth="1"/>
+    <col min="12034" max="12035" width="20.625" style="4" customWidth="1"/>
+    <col min="12036" max="12036" width="30.875" style="4" customWidth="1"/>
+    <col min="12037" max="12038" width="20.625" style="4" customWidth="1"/>
+    <col min="12039" max="12288" width="9" style="4"/>
+    <col min="12289" max="12289" width="30.875" style="4" customWidth="1"/>
+    <col min="12290" max="12291" width="20.625" style="4" customWidth="1"/>
+    <col min="12292" max="12292" width="30.875" style="4" customWidth="1"/>
+    <col min="12293" max="12294" width="20.625" style="4" customWidth="1"/>
+    <col min="12295" max="12544" width="9" style="4"/>
+    <col min="12545" max="12545" width="30.875" style="4" customWidth="1"/>
+    <col min="12546" max="12547" width="20.625" style="4" customWidth="1"/>
+    <col min="12548" max="12548" width="30.875" style="4" customWidth="1"/>
+    <col min="12549" max="12550" width="20.625" style="4" customWidth="1"/>
+    <col min="12551" max="12800" width="9" style="4"/>
+    <col min="12801" max="12801" width="30.875" style="4" customWidth="1"/>
+    <col min="12802" max="12803" width="20.625" style="4" customWidth="1"/>
+    <col min="12804" max="12804" width="30.875" style="4" customWidth="1"/>
+    <col min="12805" max="12806" width="20.625" style="4" customWidth="1"/>
+    <col min="12807" max="13056" width="9" style="4"/>
+    <col min="13057" max="13057" width="30.875" style="4" customWidth="1"/>
+    <col min="13058" max="13059" width="20.625" style="4" customWidth="1"/>
+    <col min="13060" max="13060" width="30.875" style="4" customWidth="1"/>
+    <col min="13061" max="13062" width="20.625" style="4" customWidth="1"/>
+    <col min="13063" max="13312" width="9" style="4"/>
+    <col min="13313" max="13313" width="30.875" style="4" customWidth="1"/>
+    <col min="13314" max="13315" width="20.625" style="4" customWidth="1"/>
+    <col min="13316" max="13316" width="30.875" style="4" customWidth="1"/>
+    <col min="13317" max="13318" width="20.625" style="4" customWidth="1"/>
+    <col min="13319" max="13568" width="9" style="4"/>
+    <col min="13569" max="13569" width="30.875" style="4" customWidth="1"/>
+    <col min="13570" max="13571" width="20.625" style="4" customWidth="1"/>
+    <col min="13572" max="13572" width="30.875" style="4" customWidth="1"/>
+    <col min="13573" max="13574" width="20.625" style="4" customWidth="1"/>
+    <col min="13575" max="13824" width="9" style="4"/>
+    <col min="13825" max="13825" width="30.875" style="4" customWidth="1"/>
+    <col min="13826" max="13827" width="20.625" style="4" customWidth="1"/>
+    <col min="13828" max="13828" width="30.875" style="4" customWidth="1"/>
+    <col min="13829" max="13830" width="20.625" style="4" customWidth="1"/>
+    <col min="13831" max="14080" width="9" style="4"/>
+    <col min="14081" max="14081" width="30.875" style="4" customWidth="1"/>
+    <col min="14082" max="14083" width="20.625" style="4" customWidth="1"/>
+    <col min="14084" max="14084" width="30.875" style="4" customWidth="1"/>
+    <col min="14085" max="14086" width="20.625" style="4" customWidth="1"/>
+    <col min="14087" max="14336" width="9" style="4"/>
+    <col min="14337" max="14337" width="30.875" style="4" customWidth="1"/>
+    <col min="14338" max="14339" width="20.625" style="4" customWidth="1"/>
+    <col min="14340" max="14340" width="30.875" style="4" customWidth="1"/>
+    <col min="14341" max="14342" width="20.625" style="4" customWidth="1"/>
+    <col min="14343" max="14592" width="9" style="4"/>
+    <col min="14593" max="14593" width="30.875" style="4" customWidth="1"/>
+    <col min="14594" max="14595" width="20.625" style="4" customWidth="1"/>
+    <col min="14596" max="14596" width="30.875" style="4" customWidth="1"/>
+    <col min="14597" max="14598" width="20.625" style="4" customWidth="1"/>
+    <col min="14599" max="14848" width="9" style="4"/>
+    <col min="14849" max="14849" width="30.875" style="4" customWidth="1"/>
+    <col min="14850" max="14851" width="20.625" style="4" customWidth="1"/>
+    <col min="14852" max="14852" width="30.875" style="4" customWidth="1"/>
+    <col min="14853" max="14854" width="20.625" style="4" customWidth="1"/>
+    <col min="14855" max="15104" width="9" style="4"/>
+    <col min="15105" max="15105" width="30.875" style="4" customWidth="1"/>
+    <col min="15106" max="15107" width="20.625" style="4" customWidth="1"/>
+    <col min="15108" max="15108" width="30.875" style="4" customWidth="1"/>
+    <col min="15109" max="15110" width="20.625" style="4" customWidth="1"/>
+    <col min="15111" max="15360" width="9" style="4"/>
+    <col min="15361" max="15361" width="30.875" style="4" customWidth="1"/>
+    <col min="15362" max="15363" width="20.625" style="4" customWidth="1"/>
+    <col min="15364" max="15364" width="30.875" style="4" customWidth="1"/>
+    <col min="15365" max="15366" width="20.625" style="4" customWidth="1"/>
+    <col min="15367" max="15616" width="9" style="4"/>
+    <col min="15617" max="15617" width="30.875" style="4" customWidth="1"/>
+    <col min="15618" max="15619" width="20.625" style="4" customWidth="1"/>
+    <col min="15620" max="15620" width="30.875" style="4" customWidth="1"/>
+    <col min="15621" max="15622" width="20.625" style="4" customWidth="1"/>
+    <col min="15623" max="15872" width="9" style="4"/>
+    <col min="15873" max="15873" width="30.875" style="4" customWidth="1"/>
+    <col min="15874" max="15875" width="20.625" style="4" customWidth="1"/>
+    <col min="15876" max="15876" width="30.875" style="4" customWidth="1"/>
+    <col min="15877" max="15878" width="20.625" style="4" customWidth="1"/>
+    <col min="15879" max="16128" width="9" style="4"/>
+    <col min="16129" max="16129" width="30.875" style="4" customWidth="1"/>
+    <col min="16130" max="16131" width="20.625" style="4" customWidth="1"/>
+    <col min="16132" max="16132" width="30.875" style="4" customWidth="1"/>
+    <col min="16133" max="16134" width="20.625" style="4" customWidth="1"/>
+    <col min="16135" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1"/>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7" t="s">
         <v>20</v>
-      </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="22.5" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="A3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="9" t="s">
-        <v>5</v>
+      <c r="A4" s="8" t="s">
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="11" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="E6" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="F6" s="13" t="s">
         <v>18</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1060,7 +1026,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
@@ -1070,7 +1036,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
